--- a/stories/arbres/ATOM-SEC.PAR.001-08.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Élisa arrive au parc avec papa. Les canards font coin-coin. Papa montre le bac à sable. Il dit : voici l'espace montré. Tu joues ici. Papa s'assoit sur le banc. L'adulte voit. Élisa creuse. Le sable est frais. Elle reste dans l'espace montré. Papa la voit. Un seau rouge. Une pelle. Élisa verse le sable. Plus tard, ils vont à l'aire de jeux. Le bois du pont est lisse. Papa montre le petit pont. Il dit : ici, c'est l'espace montré. Je reste là. L'adulte voit. Élisa marche sur le pont. Elle reste où papa a dit. Même leçon, autre lieu. On joue là où l'adulte a dit. L'adulte voit. Élisa dit : papa me voit. Papa hoche la tête. Ils rentrent la main dans la main.</t>
+          <t>Élisa arrive au parc avec papa. Les canards font coin-coin. Papa montre le bac à sable. Voici l'espace montré. Tu joues ici. Papa s'assoit sur le banc. L'adulte voit. Élisa creuse. Le sable est frais. Elle reste dans l'espace montré. Papa la voit. Un seau rouge. Une pelle. Élisa verse le sable. Plus tard, ils vont à l'aire de jeux. Le bois du pont est lisse. Papa montre le petit pont. Ici, c'est l'espace montré. Je reste là. L'adulte voit. Élisa marche sur le pont. Elle reste où papa a dit. Même leçon, autre lieu. On joue là où l'adulte a dit. L'adulte voit. Papa me voit. Papa hoche la tête. Ils rentrent la main dans la main.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Élisa arrive au parc avec papa. Les canards font coin-coin. Papa montre le bac à sable.
+narrateur|Voici l'espace montré. Tu joues ici. Papa s'assoit sur le banc. L'adulte voit.
+narrateur|Élisa creuse. Le sable est frais. Elle reste dans l'espace montré. Papa la voit. Un seau rouge. Une pelle. Élisa verse le sable. Plus tard, ils vont à l'aire de jeux. Le bois du pont est lisse. Papa montre le petit pont.
+narrateur|Ici, c'est l'espace montré. Je reste là. L'adulte voit.
+narrateur|Élisa marche sur le pont. Elle reste où papa a dit. Même leçon, autre lieu. On joue là où l'adulte a dit. L'adulte voit.
+enfant-f|Papa me voit. Papa hoche la tête. Ils rentrent la main dans la main.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Papa montre un espace. Où joue Élisa ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Élisa est restée dans l'espace montré. Au parc, puis à l'aire. L'adulte voit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Élisa range le seau. Papa ferme le portail.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-08.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,11 @@
 enfant-f|Papa me voit. Papa hoche la tête. Ils rentrent la main dans la main.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1512,7 @@
           <t>narrateur|Papa montre un espace. Où joue Élisa ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1684,11 @@
           <t>narrateur|Élisa est restée dans l'espace montré. Au parc, puis à l'aire. L'adulte voit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1852,7 @@
           <t>narrateur|Élisa range le seau. Papa ferme le portail.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2063,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2278,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-08.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Élisa reste où papa voit</t>
+          <t>Le pont de bois de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina joue au bac à sable puis sur le petit pont, toujours dans l'espace que papa a montré.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Élisa arrive au parc avec papa. Les canards font coin-coin. Papa montre le bac à sable. Voici l'espace montré. Tu joues ici. Papa s'assoit sur le banc. L'adulte voit. Élisa creuse. Le sable est frais. Elle reste dans l'espace montré. Papa la voit. Un seau rouge. Une pelle. Élisa verse le sable. Plus tard, ils vont à l'aire de jeux. Le bois du pont est lisse. Papa montre le petit pont. Ici, c'est l'espace montré. Je reste là. L'adulte voit. Élisa marche sur le pont. Elle reste où papa a dit. Même leçon, autre lieu. On joue là où l'adulte a dit. L'adulte voit. Papa me voit. Papa hoche la tête. Ils rentrent la main dans la main.</t>
+          <t>Les canards font des ronds dans l'eau. Une miette flotte près du bord. Le bois de la rambarde est tiède. Le parc sent l'herbe coupée. Un caillou gris brille dans la vase. Papa tient le manteau de Nina. Tu as entendu les canards, Nina ? Oui, papa. Ils font coin-coin. En ce moment, Nina arrive au bac à sable. Le sable est frais et un peu froid. Voici l'espace montré. Tu joues ici. L'adulte voit. Ici, papa ? Oui. On reste dans l'espace montré. Papa s'assoit sur le banc. Nina creuse avec la pelle. Elle reste dans l'espace montré. Papa la voit. L'adulte voit. Un seau rouge attend près du bac. Une pelle bleue est un peu rêche. Nina verse le sable, tout doux. Ça fait un tas. Un beau tas. Je te vois. Un canard s'approche du bord. L'eau clapote contre la pierre. Tu restes là où l'adulte a dit ? Oui. Dans l'espace montré. Bravo. Plus tard, ils vont à l'aire de jeux. Le bois du petit pont est lisse. Il sent le soleil et la résine. Ici, c'est l'espace montré. Je reste là, sur le banc. L'adulte voit. Je reste là. Nina marche sur le pont. Ses mains tiennent la rambarde tiède. Elle reste où papa a dit. Elle reste dans l'espace montré. Papa la voit encore. L'adulte voit. Papa me voit. Oui. Tu joues là où l'adulte a dit. Bravo, Nina. Tu as fait du bon travail. Les canards font encore coin-coin. Nina redescend du pont, tout doucement. Elle revient près du banc. Tu as fini le pont ? Oui, papa. Bravo. Ils se tiennent la main. Le bois du pont reste tiède. Nina pose la paume sur la rambarde. C'est chaud. Oui. Le soleil a chauffé le bois. Un canard plonge, tout près. L'eau fait un petit cercle. Tu es restée dans l'espace montré ? Oui, papa. Bravo. L'adulte voit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,76 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Élisa arrive au parc avec papa. Les canards font coin-coin. Papa montre le bac à sable.
-narrateur|Voici l'espace montré. Tu joues ici. Papa s'assoit sur le banc. L'adulte voit.
-narrateur|Élisa creuse. Le sable est frais. Elle reste dans l'espace montré. Papa la voit. Un seau rouge. Une pelle. Élisa verse le sable. Plus tard, ils vont à l'aire de jeux. Le bois du pont est lisse. Papa montre le petit pont.
-narrateur|Ici, c'est l'espace montré. Je reste là. L'adulte voit.
-narrateur|Élisa marche sur le pont. Elle reste où papa a dit. Même leçon, autre lieu. On joue là où l'adulte a dit. L'adulte voit.
-enfant-f|Papa me voit. Papa hoche la tête. Ils rentrent la main dans la main.</t>
+          <t>narrateur|Les canards font des ronds dans l'eau.
+narrateur|Une miette flotte près du bord.
+narrateur|Le bois de la rambarde est tiède.
+narrateur|Le parc sent l'herbe coupée.
+narrateur|Un caillou gris brille dans la vase.
+narrateur|Papa tient le manteau de Nina.
+papa|Tu as entendu les canards, Nina ?
+enfant-f|Oui, papa.
+enfant-f|Ils font coin-coin.
+narrateur|En ce moment, Nina arrive au bac à sable.
+narrateur|Le sable est frais et un peu froid.
+papa|Voici l'espace montré.
+papa|Tu joues ici.
+papa|L'adulte voit.
+enfant-f|Ici, papa ?
+papa|Oui.
+papa|On reste dans l'espace montré.
+narrateur|Papa s'assoit sur le banc.
+narrateur|Nina creuse avec la pelle.
+narrateur|Elle reste dans l'espace montré.
+narrateur|Papa la voit.
+narrateur|L'adulte voit.
+narrateur|Un seau rouge attend près du bac.
+narrateur|Une pelle bleue est un peu rêche.
+narrateur|Nina verse le sable, tout doux.
+enfant-f|Ça fait un tas.
+papa|Un beau tas.
+papa|Je te vois.
+narrateur|Un canard s'approche du bord.
+narrateur|L'eau clapote contre la pierre.
+papa|Tu restes là où l'adulte a dit ?
+enfant-f|Oui.
+enfant-f|Dans l'espace montré.
+papa|Bravo.
+narrateur|Plus tard, ils vont à l'aire de jeux.
+narrateur|Le bois du petit pont est lisse.
+narrateur|Il sent le soleil et la résine.
+papa|Ici, c'est l'espace montré.
+papa|Je reste là, sur le banc.
+papa|L'adulte voit.
+enfant-f|Je reste là.
+narrateur|Nina marche sur le pont.
+narrateur|Ses mains tiennent la rambarde tiède.
+narrateur|Elle reste où papa a dit.
+narrateur|Elle reste dans l'espace montré.
+narrateur|Papa la voit encore.
+narrateur|L'adulte voit.
+enfant-f|Papa me voit.
+papa|Oui.
+papa|Tu joues là où l'adulte a dit.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Les canards font encore coin-coin.
+narrateur|Nina redescend du pont, tout doucement.
+narrateur|Elle revient près du banc.
+papa|Tu as fini le pont ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|Ils se tiennent la main.
+narrateur|Le bois du pont reste tiède.
+narrateur|Nina pose la paume sur la rambarde.
+enfant-f|C'est chaud.
+papa|Oui.
+papa|Le soleil a chauffé le bois.
+narrateur|Un canard plonge, tout près.
+narrateur|L'eau fait un petit cercle.
+papa|Tu es restée dans l'espace montré ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|L'adulte voit.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1349,7 +1425,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Papa montre un espace. Où joue Élisa ?</t>
+          <t>Papa montre un espace. Où joue Nina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1509,7 +1585,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Papa montre un espace. Où joue Élisa ?</t>
+          <t>narrateur|Papa montre un espace.
+narrateur|Où joue Nina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1537,7 +1614,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Élisa est restée dans l'espace montré. Au parc, puis à l'aire. L'adulte voit.</t>
+          <t>Nina est restée dans l'espace montré. Au parc, puis à l'aire. L'adulte voit. Tu as joué dans l'espace montré ? Oui. Au bac, puis au pont. Bravo. L'adulte voit. Un canard secoue ses plumes.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1681,7 +1758,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Élisa est restée dans l'espace montré. Au parc, puis à l'aire. L'adulte voit.</t>
+          <t>narrateur|Nina est restée dans l'espace montré.
+narrateur|Au parc, puis à l'aire.
+narrateur|L'adulte voit.
+papa|Tu as joué dans l'espace montré ?
+enfant-f|Oui.
+enfant-f|Au bac, puis au pont.
+papa|Bravo.
+papa|L'adulte voit.
+narrateur|Un canard secoue ses plumes.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1713,7 +1798,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Élisa range le seau. Papa ferme le portail.</t>
+          <t>Nina range le seau. Le sable tombe dans le bac. Tu as fini de ranger ? Oui, papa. Bravo. Papa ferme le petit portail. Le bois claque, tout doux. Ils rentrent la main dans la main.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1849,7 +1934,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Élisa range le seau. Papa ferme le portail.</t>
+          <t>narrateur|Nina range le seau.
+narrateur|Le sable tombe dans le bac.
+papa|Tu as fini de ranger ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|Papa ferme le petit portail.
+narrateur|Le bois claque, tout doux.
+narrateur|Ils rentrent la main dans la main.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1877,7 +1969,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les canards restent sur l'eau. On a joué au pont. Oui. Dans l'espace montré. Bravo, Nina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2017,7 +2109,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Les canards restent sur l'eau.
+enfant-f|On a joué au pont.
+papa|Oui.
+papa|Dans l'espace montré.
+papa|Bravo, Nina.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2039,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2077,6 +2174,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-08.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les canards font des ronds dans l'eau. Une miette flotte près du bord. Le bois de la rambarde est tiède. Le parc sent l'herbe coupée. Un caillou gris brille dans la vase. Papa tient le manteau de Nina. Tu as entendu les canards, Nina ? Oui, papa. Ils font coin-coin. En ce moment, Nina arrive au bac à sable. Le sable est frais et un peu froid. Voici l'espace montré. Tu joues ici. L'adulte voit. Ici, papa ? Oui. On reste dans l'espace montré. Papa s'assoit sur le banc. Nina creuse avec la pelle. Elle reste dans l'espace montré. Papa la voit. L'adulte voit. Un seau rouge attend près du bac. Une pelle bleue est un peu rêche. Nina verse le sable, tout doux. Ça fait un tas. Un beau tas. Je te vois. Un canard s'approche du bord. L'eau clapote contre la pierre. Tu restes là où l'adulte a dit ? Oui. Dans l'espace montré. Bravo. Plus tard, ils vont à l'aire de jeux. Le bois du petit pont est lisse. Il sent le soleil et la résine. Ici, c'est l'espace montré. Je reste là, sur le banc. L'adulte voit. Je reste là. Nina marche sur le pont. Ses mains tiennent la rambarde tiède. Elle reste où papa a dit. Elle reste dans l'espace montré. Papa la voit encore. L'adulte voit. Papa me voit. Oui. Tu joues là où l'adulte a dit. Bravo, Nina. Tu as fait du bon travail. Les canards font encore coin-coin. Nina redescend du pont, tout doucement. Elle revient près du banc. Tu as fini le pont ? Oui, papa. Bravo. Ils se tiennent la main. Le bois du pont reste tiède. Nina pose la paume sur la rambarde. C'est chaud. Oui. Le soleil a chauffé le bois. Un canard plonge, tout près. L'eau fait un petit cercle. Tu es restée dans l'espace montré ? Oui, papa. Bravo. L'adulte voit.</t>
+          <t>Les canards font des ronds dans l'eau. Une miette flotte près du bord. Le bois de la rambarde est tiède. Le parc sent l'herbe coupée. Un caillou gris brille dans la vase. Papa tient le manteau de Nina. Tu as entendu les canards, Nina ? Oui, papa. Ils font coin-coin. En ce moment, Nina arrive au bac à sable. Le sable est frais et un peu froid. Voici l'espace montré. Tu joues ici. L'adulte voit. Ici, papa ? Oui. On reste dans l'espace montré. Papa s'assoit sur le banc. Nina creuse avec la pelle. Elle reste dans l'espace montré. Papa la voit. L'adulte voit. Un seau rouge attend près du bac. Une pelle bleue est un peu rêche. Nina verse le sable, tout doux. Ça fait un tas. Un beau tas. Je te vois. Un canard s'approche du bord. L'eau clapote contre la pierre. Tu restes là où l'adulte a dit ? Oui. Dans l'espace montré. Bravo. Plus tard, ils vont à l'aire de jeux. Le bois du petit pont est lisse. Il sent le soleil et la résine. Ici, c'est l'espace montré. Je reste là, sur le banc. L'adulte voit. Je reste là. Nina marche sur le pont. Ses mains tiennent la rambarde tiède. Elle reste où papa a dit. Elle reste dans l'espace montré. Papa la voit encore. L'adulte voit. Papa me voit. Oui. Tu joues là où l'adulte a dit. Bravo, Nina. Les canards font encore coin-coin. Nina redescend du pont, tout doucement. Elle revient près du banc. Tu as fini le pont ? Oui, papa. Bravo. Ils se tiennent la main. Le bois du pont reste tiède. Nina pose la paume sur la rambarde. C'est chaud. Oui. Le soleil a chauffé le bois. Un canard plonge, tout près. L'eau fait un petit cercle. Tu es restée dans l'espace montré ? Oui, papa. Bravo. L'adulte voit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Élisa arrive au parc avec papa. Les canards font coin-coin. Papa montre le bac à sable. Il dit : voici l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Tu joues ici. Papa s'assoit sur le banc. L'adulte voit. Élisa creuse. Le sable est frais. Elle reste dans l'espace montré. Papa la voit. Un seau rouge. Une pelle. Élisa verse le sable. Plus tard, ils vont à l'aire de jeux. Le bois du pont est lisse. Papa montre le petit pont. Il dit : ici, c'est l'espace montré. Je reste là. L'adulte voit. Élisa marche sur le pont. Elle reste où papa a dit. Même leçon, autre lieu. On joue là où l'adulte a dit. L'adulte voit. Élisa dit : papa me voit. Papa hoche la tête. Ils rentrent la main dans la main.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les canards font des ronds dans l'eau. Une miette flotte près du bord. Le bois de la rambarde est tiède. Le parc sent l'herbe coupée. Un caillou gris brille dans la vase. Papa tient le manteau de Nina. Tu as entendu les canards, Nina ? Oui, papa. Ils font coin-coin. En ce moment, Nina arrive au bac à sable. Le sable est frais et un peu froid. Voici l'espace montré. Tu joues ici. L'adulte voit. Ici, papa ? Oui. On reste dans l'espace montré. Papa s'assoit sur le banc. Nina creuse avec la pelle. Elle reste dans l'espace montré. Papa la voit. L'adulte voit. Un seau rouge attend près du bac. Une pelle bleue est un peu rêche. Nina verse le sable, tout doux. Ça fait un tas. Un beau tas. Je te vois. Un canard s'approche du bord. L'eau clapote contre la pierre. Tu restes là où l'adulte a dit ? Oui. Dans l'espace montré. Bravo. Plus tard, ils vont à l'aire de jeux. Le bois du petit pont est lisse. Il sent le soleil et la résine. Ici, c'est l'espace montré. Je reste là, sur le banc. L'adulte voit. Je reste là. Nina marche sur le pont. Ses mains tiennent la rambarde tiède. Elle reste où papa a dit. Elle reste dans l'espace montré. Papa la voit encore. L'adulte voit. Papa me voit. Oui. Tu joues là où l'adulte a dit. Bravo, Nina. Les canards font encore coin-coin. Nina redescend du pont, tout doucement. Elle revient près du banc. Tu as fini le pont ? Oui, papa. Bravo. Ils se tiennent la main. Le bois du pont reste tiède. Nina pose la paume sur la rambarde. C'est chaud. Oui. Le soleil a chauffé le bois. Un canard plonge, tout près. L'eau fait un petit cercle. Tu es restée dans l'espace montré ? Oui, papa. Bravo. L'adulte voit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1375,7 +1375,6 @@
 papa|Oui.
 papa|Tu joues là où l'adulte a dit.
 papa|Bravo, Nina.
-papa|Tu as fait du bon travail.
 narrateur|Les canards font encore coin-coin.
 narrateur|Nina redescend du pont, tout doucement.
 narrateur|Elle revient près du banc.
@@ -1430,7 +1429,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa montre un &lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt;. Où joue Élisa ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa montre un espace. Où joue Nina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1589,7 +1588,6 @@
 narrateur|Où joue Nina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1619,7 +1617,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Élisa est restée dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Au parc, puis à l'aire. L'adulte voit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina est restée dans l'espace montré. Au parc, puis à l'aire. L'adulte voit. Tu as joué dans l'espace montré ? Oui. Au bac, puis au pont. Bravo. L'adulte voit. Un canard secoue ses plumes.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1803,7 +1801,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Élisa range le seau. Papa ferme le portail.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina range le seau. Le sable tombe dans le bac. Tu as fini de ranger ? Oui, papa. Bravo. Papa ferme le petit portail. Le bois claque, tout doux. Ils rentrent la main dans la main.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1944,7 +1942,6 @@
 narrateur|Ils rentrent la main dans la main.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les canards restent sur l'eau. On a joué au pont. Oui. Dans l'espace montré. Bravo, Nina. L'histoire est finie.</t>
+          <t>Les canards restent sur l'eau. On a joué au pont. Oui. Dans l'espace montré. Bravo, Nina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les canards restent sur l'eau. On a joué au pont. Oui. Dans l'espace montré. Bravo, Nina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2113,11 +2110,9 @@
 enfant-f|On a joué au pont.
 papa|Oui.
 papa|Dans l'espace montré.
-papa|Bravo, Nina.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Nina.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2136,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2181,6 +2176,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-08.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Élisa, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
